--- a/consent_forms/049_legal_representation_authorization_form--consent_forms.xlsx
+++ b/consent_forms/049_legal_representation_authorization_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>first_name_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>First Name 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>last_name_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Last Name 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sign_date</t>
+          <t>sign_date_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sign_time</t>
+          <t>sign_time_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Sign</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Rep First Name</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Rep Last Name</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Rep Email</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
